--- a/data/file_generation/reference/data_74/筛选后的教师信息统计表_res.xlsx
+++ b/data/file_generation/reference/data_74/筛选后的教师信息统计表_res.xlsx
@@ -3520,26 +3520,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5699B83-B511-4FD8-8A1C-250B9BE91978}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51B13BEB-99D9-4362-8CB5-BC2F0B4C3D33}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE357B00-6D64-49CF-A176-6E6427773467}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C7C723E-D9D4-40AB-B257-5BB2106DE7D6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B2E784-668B-4724-BCA2-E4E54D90D6D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19D831D8-45E5-4F51-9957-179241F2845E}"/>
 </file>